--- a/db_updates/TABELA REFERENCIAL GTI 01.xlsx
+++ b/db_updates/TABELA REFERENCIAL GTI 01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\csjunior\Documents\TABELA GTI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E123961-EEE0-4257-B797-EDB92A0FAB3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B673EAA1-1754-4273-AEBA-C109B16C786E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B342AB59-AB87-4588-B4A3-317E100562A4}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B342AB59-AB87-4588-B4A3-317E100562A4}"/>
   </bookViews>
   <sheets>
     <sheet name="gti" sheetId="3" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Planilha2" sheetId="2" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">gti!$A$1:$F$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">gti!$A$1:$F$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1112" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="278">
   <si>
     <t xml:space="preserve">ELETRODUTOS </t>
   </si>
@@ -2119,6 +2119,9 @@
   </si>
   <si>
     <t>ABRAÇADEIRA 2</t>
+  </si>
+  <si>
+    <t>Abraçadeira para eletroduto de 1 3/4", inclusive bucha e parafuso</t>
   </si>
 </sst>
 </file>
@@ -2814,7 +2817,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4496DF37-853F-4F99-9368-3D75E3115958}">
-  <dimension ref="A2:F108"/>
+  <dimension ref="A2:F106"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.5703125" customWidth="1"/>
@@ -2825,7 +2828,7 @@
     <col min="6" max="6" width="39.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="25.5">
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>113</v>
       </c>
@@ -2845,7 +2848,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="25.5">
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>113</v>
       </c>
@@ -3067,42 +3070,36 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B14" s="20">
+        <v>150904</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>277</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B15" s="20" t="s">
         <v>224</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C15" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="D15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>169</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F15" s="5" t="s">
         <v>169</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>227</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -3110,39 +3107,39 @@
         <v>4</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E16" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="20" t="s">
+        <v>228</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F17" s="5" t="s">
         <v>85</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="20" t="s">
-        <v>230</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -3150,19 +3147,19 @@
         <v>4</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -3170,10 +3167,10 @@
         <v>4</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>2</v>
@@ -3186,23 +3183,23 @@
       </c>
     </row>
     <row r="20" spans="1:6">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>235</v>
-      </c>
-      <c r="D20" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D20" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>167</v>
+        <v>1</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>167</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -3210,19 +3207,19 @@
         <v>4</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>104</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -3230,19 +3227,19 @@
         <v>4</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -3250,19 +3247,19 @@
         <v>4</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>240</v>
+        <v>222</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -3270,19 +3267,19 @@
         <v>4</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -3290,10 +3287,10 @@
         <v>4</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>7</v>
@@ -3306,23 +3303,23 @@
       </c>
     </row>
     <row r="26" spans="1:6">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B26" s="20" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="D26" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>7</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -3330,19 +3327,19 @@
         <v>4</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -3350,79 +3347,79 @@
         <v>4</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>7</v>
       </c>
       <c r="E28" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
+      <c r="A29" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="20" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="20" t="s">
-        <v>251</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>252</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" s="1" customFormat="1" ht="12.75">
+    <row r="30" spans="1:6">
       <c r="A30" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B30" s="20" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" s="1" customFormat="1" ht="12.75">
       <c r="A31" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B31" s="20" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>174</v>
+        <v>9</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>174</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -3430,19 +3427,19 @@
         <v>4</v>
       </c>
       <c r="B32" s="20" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -3450,19 +3447,19 @@
         <v>4</v>
       </c>
       <c r="B33" s="20" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>153</v>
+        <v>176</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -3470,19 +3467,19 @@
         <v>4</v>
       </c>
       <c r="B34" s="20" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>98</v>
+        <v>153</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -3490,19 +3487,19 @@
         <v>4</v>
       </c>
       <c r="B35" s="20" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>13</v>
+        <v>98</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -3510,19 +3507,19 @@
         <v>4</v>
       </c>
       <c r="B36" s="20" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -3530,24 +3527,30 @@
         <v>4</v>
       </c>
       <c r="B37" s="20" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>268</v>
-      </c>
-      <c r="D37" s="2"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
+        <v>266</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B38" s="20" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="D38" s="2"/>
       <c r="E38" s="5"/>
@@ -3555,13 +3558,13 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B39" s="22" t="s">
-        <v>275</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>276</v>
+        <v>4</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>270</v>
       </c>
       <c r="D39" s="2"/>
       <c r="E39" s="5"/>
@@ -3569,83 +3572,101 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B40" s="3">
-        <v>20303</v>
-      </c>
-      <c r="C40" s="4"/>
+        <v>214</v>
+      </c>
+      <c r="B40" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="C40" s="23" t="s">
+        <v>276</v>
+      </c>
       <c r="D40" s="2"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B41" s="3">
-        <v>20304</v>
-      </c>
-      <c r="C41" s="4"/>
+        <v>214</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>273</v>
+      </c>
       <c r="D41" s="2"/>
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="3">
-        <v>20305</v>
-      </c>
-      <c r="C42" s="4"/>
-      <c r="D42" s="2"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
+        <v>214</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>212</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>274</v>
+      <c r="B43" s="17" t="s">
+        <v>213</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="D43" s="2"/>
-      <c r="E43" s="5"/>
-      <c r="F43" s="5"/>
+        <v>216</v>
+      </c>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>212</v>
+        <v>191</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="D44" s="9"/>
-      <c r="E44" s="9"/>
-      <c r="F44" s="9"/>
-    </row>
-    <row r="45" spans="1:6">
+        <v>192</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" s="1" customFormat="1">
       <c r="A45" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>213</v>
+        <v>191</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>191</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="D45" s="9"/>
-      <c r="E45" s="9"/>
-      <c r="F45" s="9"/>
-    </row>
-    <row r="46" spans="1:6">
+        <v>193</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" s="1" customFormat="1">
       <c r="A46" s="2" t="s">
         <v>191</v>
       </c>
@@ -3653,7 +3674,7 @@
         <v>191</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D46" s="9" t="s">
         <v>204</v>
@@ -3665,7 +3686,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="47" spans="1:6" s="1" customFormat="1">
+    <row r="47" spans="1:6">
       <c r="A47" s="2" t="s">
         <v>191</v>
       </c>
@@ -3673,7 +3694,7 @@
         <v>191</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D47" s="9" t="s">
         <v>204</v>
@@ -3685,7 +3706,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="48" spans="1:6" s="1" customFormat="1">
+    <row r="48" spans="1:6">
       <c r="A48" s="2" t="s">
         <v>191</v>
       </c>
@@ -3693,7 +3714,7 @@
         <v>191</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D48" s="9" t="s">
         <v>204</v>
@@ -3713,7 +3734,7 @@
         <v>191</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>204</v>
@@ -3733,7 +3754,7 @@
         <v>191</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D50" s="9" t="s">
         <v>204</v>
@@ -3753,7 +3774,7 @@
         <v>191</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D51" s="9" t="s">
         <v>204</v>
@@ -3773,7 +3794,7 @@
         <v>191</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D52" s="9" t="s">
         <v>204</v>
@@ -3793,7 +3814,7 @@
         <v>191</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>204</v>
@@ -3813,7 +3834,7 @@
         <v>191</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="D54" s="9" t="s">
         <v>204</v>
@@ -3833,7 +3854,7 @@
         <v>191</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>204</v>
@@ -3853,7 +3874,7 @@
         <v>191</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D56" s="9" t="s">
         <v>204</v>
@@ -3873,7 +3894,7 @@
         <v>191</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D57" s="9" t="s">
         <v>204</v>
@@ -3893,7 +3914,7 @@
         <v>191</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D58" s="9" t="s">
         <v>204</v>
@@ -3913,7 +3934,7 @@
         <v>191</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>204</v>
@@ -3929,11 +3950,11 @@
       <c r="A60" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B60" s="2" t="s">
+      <c r="B60" s="17" t="s">
         <v>191</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D60" s="9" t="s">
         <v>204</v>
@@ -3949,11 +3970,11 @@
       <c r="A61" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="B61" s="2" t="s">
+      <c r="B61" s="17" t="s">
         <v>191</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>219</v>
+        <v>271</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>204</v>
@@ -3973,7 +3994,7 @@
         <v>191</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>204</v>
@@ -3987,42 +4008,42 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>191</v>
+        <v>18</v>
+      </c>
+      <c r="B63" s="3">
+        <v>150612</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="D63" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="E63" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="F63" s="9" t="s">
-        <v>206</v>
+        <v>152</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:6">
       <c r="A64" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B64" s="17" t="s">
-        <v>191</v>
+        <v>18</v>
+      </c>
+      <c r="B64" s="3">
+        <v>150632</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D64" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="E64" s="9" t="s">
-        <v>205</v>
-      </c>
-      <c r="F64" s="9" t="s">
-        <v>206</v>
+        <v>149</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -4030,107 +4051,91 @@
         <v>18</v>
       </c>
       <c r="B65" s="3">
-        <v>150612</v>
+        <v>150633</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="66" spans="1:6">
-      <c r="A66" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B66" s="3">
-        <v>150632</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F66" s="5" t="s">
-        <v>147</v>
+      <c r="A66" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B66" s="9">
+        <v>160872</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E66" s="13">
+        <v>28</v>
+      </c>
+      <c r="F66" s="13">
+        <v>37.42</v>
       </c>
     </row>
     <row r="67" spans="1:6">
-      <c r="A67" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B67" s="3">
-        <v>150633</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>144</v>
+      <c r="A67" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B67" s="9">
+        <v>160872</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>187</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E67" s="12">
+        <v>44.18</v>
+      </c>
+      <c r="F67" s="12">
+        <v>58.87</v>
       </c>
     </row>
     <row r="68" spans="1:6">
-      <c r="A68" s="9" t="s">
+      <c r="A68" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B68" s="9">
-        <v>160872</v>
-      </c>
-      <c r="C68" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="D68" s="9" t="s">
-        <v>186</v>
-      </c>
-      <c r="E68" s="13">
-        <v>28</v>
-      </c>
-      <c r="F68" s="13">
-        <v>37.42</v>
-      </c>
+      <c r="B68" s="19">
+        <v>180201</v>
+      </c>
+      <c r="C68" s="4"/>
+      <c r="D68" s="2"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="A69" s="9" t="s">
+      <c r="A69" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="B69" s="9">
-        <v>160872</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E69" s="12">
-        <v>44.18</v>
-      </c>
-      <c r="F69" s="12">
-        <v>58.87</v>
-      </c>
+      <c r="B69" s="19">
+        <v>180202</v>
+      </c>
+      <c r="C69" s="4"/>
+      <c r="D69" s="2"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
     </row>
     <row r="70" spans="1:6">
       <c r="A70" s="2" t="s">
         <v>184</v>
       </c>
       <c r="B70" s="19">
-        <v>180201</v>
+        <v>151401</v>
       </c>
       <c r="C70" s="4"/>
       <c r="D70" s="2"/>
@@ -4142,7 +4147,7 @@
         <v>184</v>
       </c>
       <c r="B71" s="19">
-        <v>180202</v>
+        <v>151402</v>
       </c>
       <c r="C71" s="4"/>
       <c r="D71" s="2"/>
@@ -4154,7 +4159,7 @@
         <v>184</v>
       </c>
       <c r="B72" s="19">
-        <v>151401</v>
+        <v>151403</v>
       </c>
       <c r="C72" s="4"/>
       <c r="D72" s="2"/>
@@ -4166,7 +4171,7 @@
         <v>184</v>
       </c>
       <c r="B73" s="19">
-        <v>151402</v>
+        <v>151404</v>
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="2"/>
@@ -4178,7 +4183,7 @@
         <v>184</v>
       </c>
       <c r="B74" s="19">
-        <v>151403</v>
+        <v>151405</v>
       </c>
       <c r="C74" s="4"/>
       <c r="D74" s="2"/>
@@ -4187,46 +4192,62 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B75" s="19">
-        <v>151404</v>
-      </c>
-      <c r="C75" s="4"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="5"/>
-      <c r="F75" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="B75" s="3">
+        <v>160869</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E75" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="76" spans="1:6">
       <c r="A76" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B76" s="19">
-        <v>151405</v>
-      </c>
-      <c r="C76" s="4"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
+        <v>18</v>
+      </c>
+      <c r="B76" s="3">
+        <v>160870</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E76" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B77" s="3">
-        <v>160869</v>
+        <v>160847</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>122</v>
+        <v>27</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>120</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -4234,39 +4255,39 @@
         <v>18</v>
       </c>
       <c r="B78" s="3">
-        <v>160870</v>
+        <v>160848</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>119</v>
+        <v>24</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>117</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79" spans="1:6">
-      <c r="A79" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B79" s="3">
-        <v>160847</v>
+      <c r="A79" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B79" s="8">
+        <v>160807</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D79" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>2</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>25</v>
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -4274,119 +4295,119 @@
         <v>18</v>
       </c>
       <c r="B80" s="3">
-        <v>160848</v>
+        <v>160851</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>22</v>
+        <v>78</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="F80" s="12" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="81" spans="1:6">
-      <c r="A81" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B81" s="8">
-        <v>160807</v>
+      <c r="A81" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B81" s="3">
+        <v>160839</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="F81" s="5" t="s">
-        <v>106</v>
+        <v>188</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E81" s="12">
+        <v>5.3</v>
+      </c>
+      <c r="F81" s="12">
+        <v>7.06</v>
       </c>
     </row>
     <row r="82" spans="1:6">
-      <c r="A82" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B82" s="3">
-        <v>160851</v>
+      <c r="A82" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B82" s="8">
+        <v>160872</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="D82" s="11" t="s">
-        <v>190</v>
-      </c>
-      <c r="E82" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F82" s="12" t="s">
-        <v>76</v>
+        <v>84</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="83" spans="1:6">
-      <c r="A83" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="B83" s="3">
-        <v>160839</v>
+      <c r="A83" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B83" s="8">
+        <v>160873</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E83" s="12">
-        <v>5.3</v>
-      </c>
-      <c r="F83" s="12">
-        <v>7.06</v>
+        <v>81</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="E83" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="84" spans="1:6">
-      <c r="A84" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B84" s="8">
-        <v>160872</v>
+      <c r="A84" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B84" s="3">
+        <v>160809</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D84" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
     </row>
     <row r="85" spans="1:6">
-      <c r="A85" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B85" s="8">
-        <v>160873</v>
+      <c r="A85" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B85" s="3">
+        <v>160810</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D85" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -4394,19 +4415,19 @@
         <v>18</v>
       </c>
       <c r="B86" s="3">
-        <v>160809</v>
+        <v>160811</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -4414,19 +4435,19 @@
         <v>18</v>
       </c>
       <c r="B87" s="3">
-        <v>160810</v>
+        <v>160812</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -4434,19 +4455,19 @@
         <v>18</v>
       </c>
       <c r="B88" s="3">
-        <v>160811</v>
+        <v>160813</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -4454,19 +4475,19 @@
         <v>18</v>
       </c>
       <c r="B89" s="3">
-        <v>160812</v>
+        <v>160814</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -4474,19 +4495,19 @@
         <v>18</v>
       </c>
       <c r="B90" s="3">
-        <v>160813</v>
+        <v>160815</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -4494,19 +4515,19 @@
         <v>18</v>
       </c>
       <c r="B91" s="3">
-        <v>160814</v>
+        <v>160816</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -4514,19 +4535,19 @@
         <v>18</v>
       </c>
       <c r="B92" s="3">
-        <v>160815</v>
+        <v>160825</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -4534,19 +4555,19 @@
         <v>18</v>
       </c>
       <c r="B93" s="3">
-        <v>160816</v>
+        <v>160826</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -4554,19 +4575,19 @@
         <v>18</v>
       </c>
       <c r="B94" s="3">
-        <v>160825</v>
+        <v>160827</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -4574,19 +4595,19 @@
         <v>18</v>
       </c>
       <c r="B95" s="3">
-        <v>160826</v>
+        <v>160828</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -4594,19 +4615,19 @@
         <v>18</v>
       </c>
       <c r="B96" s="3">
-        <v>160827</v>
+        <v>160834</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>45</v>
+        <v>166</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>44</v>
+        <v>165</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>43</v>
+        <v>164</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -4614,19 +4635,19 @@
         <v>18</v>
       </c>
       <c r="B97" s="3">
-        <v>160828</v>
+        <v>160833</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>42</v>
+        <v>163</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>41</v>
+        <v>162</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>40</v>
+        <v>161</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -4634,19 +4655,19 @@
         <v>18</v>
       </c>
       <c r="B98" s="3">
-        <v>160834</v>
+        <v>160831</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -4654,99 +4675,99 @@
         <v>18</v>
       </c>
       <c r="B99" s="3">
-        <v>160833</v>
+        <v>160832</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="25.5">
       <c r="A100" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B100" s="3">
-        <v>160831</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>160</v>
+        <v>160866</v>
+      </c>
+      <c r="C100" s="10" t="s">
+        <v>39</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>159</v>
+        <v>38</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" ht="25.5">
       <c r="A101" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B101" s="3">
-        <v>160832</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>157</v>
+        <v>160867</v>
+      </c>
+      <c r="C101" s="10" t="s">
+        <v>36</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>156</v>
+        <v>35</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" ht="25.5">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B102" s="3">
-        <v>160866</v>
-      </c>
-      <c r="C102" s="10" t="s">
-        <v>39</v>
+        <v>160829</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="25.5">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B103" s="3">
-        <v>160867</v>
-      </c>
-      <c r="C103" s="10" t="s">
-        <v>36</v>
+        <v>160830</v>
+      </c>
+      <c r="C103" s="18" t="s">
+        <v>30</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -4754,19 +4775,19 @@
         <v>18</v>
       </c>
       <c r="B104" s="3">
-        <v>160829</v>
-      </c>
-      <c r="C104" s="4" t="s">
-        <v>33</v>
+        <v>160822</v>
+      </c>
+      <c r="C104" s="18" t="s">
+        <v>143</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>32</v>
+        <v>142</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>31</v>
+        <v>141</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -4774,75 +4795,35 @@
         <v>18</v>
       </c>
       <c r="B105" s="3">
-        <v>160830</v>
+        <v>160823</v>
       </c>
       <c r="C105" s="18" t="s">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>29</v>
+        <v>139</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
     </row>
     <row r="106" spans="1:6">
-      <c r="A106" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B106" s="3">
-        <v>160822</v>
-      </c>
-      <c r="C106" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E106" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="F106" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6">
-      <c r="A107" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B107" s="3">
-        <v>160823</v>
-      </c>
-      <c r="C107" s="18" t="s">
-        <v>140</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E107" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="F107" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6">
-      <c r="A108" s="16" t="s">
+      <c r="A106" s="16" t="s">
         <v>203</v>
       </c>
-      <c r="B108" s="16"/>
-      <c r="C108" s="16"/>
-      <c r="D108" s="16"/>
-      <c r="E108" s="16"/>
-      <c r="F108" s="16"/>
+      <c r="B106" s="16"/>
+      <c r="C106" s="16"/>
+      <c r="D106" s="16"/>
+      <c r="E106" s="16"/>
+      <c r="F106" s="16"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F108" xr:uid="{4496DF37-853F-4F99-9368-3D75E3115958}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F108">
-      <sortCondition descending="1" ref="A1:A108"/>
+  <autoFilter ref="A1:F106" xr:uid="{4496DF37-853F-4F99-9368-3D75E3115958}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F106">
+      <sortCondition descending="1" ref="A1:A106"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.11811023622047245" right="0.11811023622047245" top="0" bottom="0" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7518,6 +7499,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="c407d157-dc1b-452d-8e32-fa12cc106a55" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010033EEAB3C55E6B245B0485CBB9EAF5AAF" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1209ea68121d0676ce616169cfff7909">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="c407d157-dc1b-452d-8e32-fa12cc106a55" xmlns:ns4="76847fb8-0a43-4b94-bd74-9898486c1b7b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6668b3feb1510deea7dc166534bf5b7d" ns3:_="" ns4:_="">
     <xsd:import namespace="c407d157-dc1b-452d-8e32-fa12cc106a55"/>
@@ -7744,24 +7742,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE752A47-FD37-4E87-A4C6-C77C48480B08}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c407d157-dc1b-452d-8e32-fa12cc106a55"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="76847fb8-0a43-4b94-bd74-9898486c1b7b"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="c407d157-dc1b-452d-8e32-fa12cc106a55" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EE000D3-B153-437F-833B-B6ABC895B888}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B1231FC-487B-4554-8B0C-0C86E8797B79}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7778,29 +7784,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9EE000D3-B153-437F-833B-B6ABC895B888}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE752A47-FD37-4E87-A4C6-C77C48480B08}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c407d157-dc1b-452d-8e32-fa12cc106a55"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="76847fb8-0a43-4b94-bd74-9898486c1b7b"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>